--- a/viveprop-platform/data/cc_data.xlsx
+++ b/viveprop-platform/data/cc_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF77"/>
+  <dimension ref="A1:BI78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,135 +574,150 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>Pie mínimo</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>Financiamiento</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Cuotas prog.</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Getnet (cuotas)</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Alt. pie 10%</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Fecha ult. cuota</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Descuento RVC</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Promociones</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Condiciones</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Pre/Aprobación bancaria</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Monto Reserva</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Pie minimo %</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Cuotas</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Monto Contra promesa</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Forma de pago cuotas</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Fecha máxima de pago pie</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Condición Estacionamientos</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Condición Bodegas</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Descuento autorizado</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Valor reserva</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Fecha escrituración</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>N° cuotas const.</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Descuento máximo</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>% cuotas const.</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Contra promesa</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Fecha máx. cuota</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Desc. adic. cierre</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
@@ -721,7 +736,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2027 - S2</t>
+          <t>2.028</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -736,22 +751,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>500.000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -769,7 +784,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -784,7 +799,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2028 - S2</t>
+          <t>2.029</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -794,27 +809,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>500.000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -832,7 +847,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BF3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,7 +862,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2028 - S1</t>
+          <t>2.028</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -857,27 +872,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>500.000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -895,7 +910,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -910,7 +925,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2028 - S2</t>
+          <t>2.029</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -940,7 +955,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -958,7 +973,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -973,7 +988,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2028 - S2</t>
+          <t>2.029</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -983,27 +998,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>500.000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1021,70 +1036,75 @@
           <t>No</t>
         </is>
       </c>
-      <c r="BF6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2% SurOriente</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>proj_alto-buzeta-mt</t>
+          <t>proj_distrito-centro</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alto Buzeta (MT)</t>
+          <t>Distrito Centro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pre-entrega</t>
+          <t>2.029</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cerrillos</t>
+          <t>Chillán</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>500.000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>UF 7,0</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>500.000</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>3% 3D</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1094,492 +1114,313 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pintor Cicarelli I: solo tipología 3D1B (con descuento máximo de venta de 12%)</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr"/>
+          <t>Pintor Cicarelli I: solo tipología 3D1B (con descuento máximo de venta de 10%)</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>proj_caceres</t>
+          <t>proj_alto-buzeta-mt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cáceres</t>
+          <t>Alto Buzeta</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>09/02/2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr"/>
+          <t>22.22%</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>proj_jardines-de-alvarado</t>
+          <t>proj_caceres</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jardines de Alvarado: solo tipología 3D1B (con descuento máximo de venta de 12%)</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr"/>
+          <t>Cáceres</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>27/02/2024</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>proj_mirador-mapocho</t>
+          <t>proj_jardines-de-alvarado</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mirador Mapocho: solo tipología 1D1B (con descuento máximo de venta de 7%)</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr"/>
+          <t>Jardines de Alvarado</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15/02/2023</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>proj_pintor-cicarelli-ii</t>
+          <t>proj_mirador-mapocho</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pintor Cicarelli II</t>
+          <t>Mirador Mapocho</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inmediata</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>San Joaquín</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr"/>
+          <t>Vivienda Social</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>proj_plaza-cervantes-i</t>
+          <t>proj_pintor-cicarelli-ii</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Plaza Cervantes I</t>
+          <t>Pintor Cicarelli II</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>06/07/2023</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr"/>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>proj_plaza-cervantes-ii</t>
+          <t>proj_plaza-cervantes-i</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Plaza Cervantes II</t>
+          <t>Plaza Cervantes I</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>03/04/2023</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr"/>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>proj_plaza-quilicura</t>
+          <t>proj_plaza-cervantes-ii</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Plaza Quilicura</t>
+          <t>Plaza Cervantes II</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>03/04/2023</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Quilicura</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2% 2D (36m2)</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr"/>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>proj_trinidad-iii</t>
+          <t>proj_plaza-quilicura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trinidad III</t>
+          <t>Plaza Quilicura</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>24/02/2023</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>500.000</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr"/>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>proj_vista-costanera</t>
+          <t>proj_trinidad-iii</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vista Costanera</t>
+          <t>Trinidad III</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>31/12/2021</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Renca</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>500.000</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr"/>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>proj_vista-reloncavi</t>
+          <t>proj_vista-costanera</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vista Reloncaví</t>
+          <t>Vista Costanera</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>14/09/2022</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Max 10%</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2% 3D</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr"/>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>proj_santa-isabel</t>
+          <t>proj_vista-reloncavi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Santa Isabel (STI)</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Entrega inmediata</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>100.000</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>15,0%</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>1 a 1</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
-        </is>
-      </c>
+          <t>Vista Reloncaví</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>26/11/2024</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1604,7 +1445,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -1614,17 +1455,17 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -1632,22 +1473,23 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas
- 1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
+1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses
+Gift Card de $200.000 por escritura en unidad principal y de $300.000 por unidad principal + estacionamiento y bodega</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>proj_santa-rosa</t>
+          <t>proj_tocornal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Santa Rosa (SRO)</t>
+          <t>Tocornal (TOC)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -1662,7 +1504,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -1672,12 +1514,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -1685,21 +1527,22 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses
+Venta de depto + estacionamiento + bodega con gift card para el broker de $1.000.000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>proj_tocornal</t>
+          <t>proj_santos-ossa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tocornal (TOC)</t>
+          <t>Santos Ossa (OSSA)</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -1712,9 +1555,14 @@
           <t>100.000</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -1724,12 +1572,17 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -1737,22 +1590,22 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses
- Venta de depto + estacionamiento + bodega con gift card para el broker de $1.000.000</t>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>No aplica a beneficios DFL2
+Crédito en hasta 36 cuotas. Gift Card de $1.000.000 para el broker</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>proj_santos-ossa</t>
+          <t>proj_los-alerces</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Santos Ossa (OSSA)</t>
+          <t>Los Alerces (ALE)</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -1765,14 +1618,9 @@
           <t>100.000</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -1782,17 +1630,17 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -1800,22 +1648,23 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>No aplica a beneficios DFL2
- Crédito en hasta 36 cuotas. Gift Card de $1.000.000 para el broker</t>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>Crédito en hasta 36 cuotas
+1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses
+Gift Card de $200.000 por escritura en unidad principal y de $300.000 por unidad principal + estacionamiento y bodega</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>proj_los-alerces</t>
+          <t>proj_bellavista</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Los Alerces (ALE)</t>
+          <t>Bellavista (BEL)</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -1830,7 +1679,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -1840,17 +1689,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>5,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -1858,22 +1702,22 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF24" t="inlineStr">
-        <is>
-          <t>Crédito en hasta 36 cuotas
- 1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses
+Gift Card de $200.000 por escritura en unidad principal y de $300.000 por unidad principal + estacionamiento y bodega</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>proj_bellavista</t>
+          <t>proj_froilan-roa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bellavista (BEL)</t>
+          <t>Froilan Roa (ROA)</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -1888,7 +1732,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -1898,12 +1742,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -1911,7 +1755,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BI25" t="inlineStr">
         <is>
           <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
         </is>
@@ -1920,12 +1764,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>proj_froilan-roa</t>
+          <t>proj_centenario-i</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Froilan Roa (ROA)</t>
+          <t>Centenario I (FRK)</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -1940,7 +1784,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -1948,14 +1792,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -1963,7 +1802,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF26" t="inlineStr">
+      <c r="BI26" t="inlineStr">
         <is>
           <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
         </is>
@@ -1972,12 +1811,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>proj_centenario-i</t>
+          <t>proj_valle-los-ingleses</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Centenario I (FRK)</t>
+          <t>Valle los Ingleses (ING)</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -1992,7 +1831,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2005,26 +1844,26 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF27" t="inlineStr">
-        <is>
-          <t>1er arriendo sin comisión de corretaje o 3 meses de administración asegurada contratando plan black por 18 meses</t>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>No aplica a beneficios DFL2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>proj_valle-los-ingleses</t>
+          <t>proj_vespucio-capital</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Valle los Ingleses (ING)</t>
+          <t>Vespucio Capital (VESP)</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Entrega inmediata</t>
+          <t>Entrega Inmediata</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2034,7 +1873,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2042,31 +1881,38 @@
           <t>1</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
       <c r="Y28" t="inlineStr">
         <is>
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>No aplica a beneficios DFL2</t>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>Crédito y arriendo garantizado en paralaleo hasta el 30/06/2031)
+Para aprobaciones al 90% el 10% de aporte se debe usar OBLIGATORIAMENTE como descuento
+Gift card de $100.000 en caso de financiamiento con BCI o Santander</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>proj_vespucio-capital</t>
+          <t>proj_vivaceta</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vespucio Capital (VESP)</t>
+          <t>Vivaceta (VTA)</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Entrega Inmediata</t>
+          <t>2do semestre 2027</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2076,22 +1922,27 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -2099,21 +1950,21 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>Crédito en 63 cuotas con arriendo garantizado (Arriendo hasta el 30/06/2031)</t>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>Crédito en hasta 36 cuotas</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>proj_vivaceta</t>
+          <t>proj_vicuna-mackenna-7589-i</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vivaceta (VTA)</t>
+          <t>Vicuña Mackenna 7589 (VIC y VIC2)</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2126,24 +1977,29 @@
           <t>100.000</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -2151,7 +2007,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF30" t="inlineStr">
+      <c r="BI30" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2160,12 +2016,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>proj_vicuna-mackenna-7589-i</t>
+          <t>proj_vicuna-mackenna-7589-ii</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vicuña Mackenna 7589 I y II (VIC) (VIC2)</t>
+          <t>Vicuña Mackenna 7589 (VIC y VIC2)</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2178,24 +2034,29 @@
           <t>100.000</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -2203,7 +2064,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF31" t="inlineStr">
+      <c r="BI31" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2212,12 +2073,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>proj_vicuna-mackenna-7589-ii</t>
+          <t>proj_diagonal-paraguay</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vicuña Mackenna 7589 I y II (VIC) (VIC2)</t>
+          <t>Diagonal Paraguay (DP)</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -2232,22 +2093,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>6,0%</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>5,0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -2255,26 +2111,22 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF32" t="inlineStr">
-        <is>
-          <t>Crédito en hasta 36 cuotas</t>
-        </is>
-      </c>
+      <c r="BI32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>proj_diagonal-paraguay</t>
+          <t>proj_abdon-cifuentes</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Diagonal Paraguay (DP)</t>
+          <t>Abdón Cifuentes (ABD)</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2do semestre 2027</t>
+          <t>1er semestre 2028</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2284,17 +2136,22 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -2302,22 +2159,26 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF33" t="inlineStr"/>
+      <c r="BI33" t="inlineStr">
+        <is>
+          <t>Crédito en hasta 36 cuotas</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>proj_abdon-cifuentes</t>
+          <t>proj_don-ignacio</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abdón Cifuentes (ABD)</t>
+          <t>Don Ignacio (DOM)</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1er semestre 2028</t>
+          <t>2do semestre 2028</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -2327,22 +2188,22 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -2350,7 +2211,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF34" t="inlineStr">
+      <c r="BI34" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2359,17 +2220,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>proj_don-ignacio</t>
+          <t>proj_los-lilenes</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Don Ignacio (DOM)</t>
+          <t>Los Lilenes (LEN)</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2do semestre 2028</t>
+          <t>1er semestre 2029</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2379,22 +2240,22 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -2402,7 +2263,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF35" t="inlineStr">
+      <c r="BI35" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2411,17 +2272,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>proj_los-lilenes</t>
+          <t>proj_coronel-godoy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Los Lilenes (LEN)</t>
+          <t>Coronel Godoy (GOD)</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1er semestre 2029</t>
+          <t>2do semestre 2028</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -2429,24 +2290,29 @@
           <t>100.000</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>21</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -2454,26 +2320,26 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF36" t="inlineStr">
-        <is>
-          <t>Crédito en hasta 36 cuotas</t>
+      <c r="BI36" t="inlineStr">
+        <is>
+          <t>Crédito en hasta 12 cuotas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>proj_coronel-godoy</t>
+          <t>proj_nueva-esmeralda</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coronel Godoy (GOD)</t>
+          <t>Nueva Esmeralda (NES)</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2do semestre 2028</t>
+          <t>2do semestre 2027</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -2483,7 +2349,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13%</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -2493,12 +2359,12 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -2506,26 +2372,26 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>Crédito en hasta 12 cuotas</t>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>Crédito en hasta 24 cuotas</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>proj_nueva-esmeralda</t>
+          <t>proj_brasil</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nueva Esmeralda (NES)</t>
+          <t>Brasil (BRA)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2do semestre 2027</t>
+          <t>1er semestre 2029</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -2533,24 +2399,29 @@
           <t>100.000</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -2558,26 +2429,26 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF38" t="inlineStr">
-        <is>
-          <t>Crédito en hasta 24 cuotas</t>
+      <c r="BI38" t="inlineStr">
+        <is>
+          <t>Crédito en hasta 36 cuotas</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>proj_brasil</t>
+          <t>proj_terrazzo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Brasil (BRA)</t>
+          <t>Terrazzo (TER)</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>1er semestre 2029</t>
+          <t>2do semestre 2028</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -2585,24 +2456,29 @@
           <t>100.000</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>31</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
@@ -2610,7 +2486,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF39" t="inlineStr">
+      <c r="BI39" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2619,17 +2495,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>proj_terrazzo</t>
+          <t>proj_el-aromo</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Terrazzo (TER)</t>
+          <t>El Aromo (ARO)</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2do semestre 2028</t>
+          <t>2do semestre 2027</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -2639,27 +2515,27 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
@@ -2667,7 +2543,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF40" t="inlineStr">
+      <c r="BI40" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2676,17 +2552,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>proj_el-aromo</t>
+          <t>proj_matta</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>El Aromo (ARO)</t>
+          <t>Matta (MAT)</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2do semestre 2027</t>
+          <t>1er semestre 2029</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -2696,27 +2572,27 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>36</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
@@ -2724,7 +2600,7 @@
           <t>1 a 1</t>
         </is>
       </c>
-      <c r="BF41" t="inlineStr">
+      <c r="BI41" t="inlineStr">
         <is>
           <t>Crédito en hasta 36 cuotas</t>
         </is>
@@ -2733,112 +2609,126 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>proj_matta</t>
+          <t>proj_condominio-parque-del-sur-torre-a</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Matta (MAT)</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>1er semestre 2029</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>100.000</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>1 a 1</t>
-        </is>
-      </c>
-      <c r="BF42" t="inlineStr">
-        <is>
-          <t>Crédito en hasta 36 cuotas</t>
+          <t>Condominio Parque del Sur torre A</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>La Cisterna</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Inmediata</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>Aprobación</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI42" t="inlineStr">
+        <is>
+          <t>Estacionamientos desde 2D2B en adelante y Bodega disponible desde 2D1B en adelante, Deptos (202,203,207,208,209) van con Anexo 60 Dias</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>proj_alto-maranon-3</t>
+          <t>proj_edificio-castillo-urizar</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alto Marañon 3</t>
+          <t>Edificio Castillo Urizar</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Ñuñoa</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AG43" t="inlineStr">
+      <c r="AH43" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>1. SOLO LÍNEA 5 DISPONIBLE
- 2. Estacionamiento solo 3D/2B
- 3. Depto. 204 on anexo de 60 dias
- 4. No se pueden vender BD y EST por separado</t>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL43" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI43" t="inlineStr">
+        <is>
+          <t>1. Estacionamiento y bodega obligatoria 
+2. Depto 1110 no va con subsidio a la tasa 
+3.Anexo 60 dias para todas las unidades</t>
         </is>
       </c>
     </row>
@@ -2855,164 +2745,202 @@
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>Estacion central</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AG44" t="inlineStr">
+      <c r="AH44" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF44" t="inlineStr">
-        <is>
-          <t>1. Sin estacionamiento y bodegas disponibles
- 2. Anexo 60 dias todas las unidades</t>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL44" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI44" t="inlineStr">
+        <is>
+          <t>1. Sin estacionamientos ni bodegas disponibles
+2.Anexo 60 dias para todas las unidades</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>proj_edificio-trinidad-ramirez</t>
+          <t>proj_condominio-francisco-zelada-torre-a</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Edificio Trinidad Ramirez</t>
+          <t>Edificio Francisco Zelada Torre A</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Futura</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Aprobación</t>
+          <t>10% o lo que no financie el Banco</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Pre Aprobación</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>28/02/2027</t>
+          <t>53 (17+36)</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF45" t="inlineStr">
-        <is>
-          <t>1. Estacionamiento debe ser vendido junto con la ultima unidad disponible
- 2,Bodega obligatoria
- 2. Todas las unidades llevan anexo 60 días</t>
+          <t>En 53 cuotas (5% en 17 + 5% en 36):
+17 cuotas + 1 cuoton final con getnet hasta en 36 cuotas</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>30/09/2027</t>
+        </is>
+      </c>
+      <c r="AL45" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Arriendo Asegurado 24m, Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI45" t="inlineStr">
+        <is>
+          <t>Estacionamiento solo para 2D/2B
+ Bodega 2D/1B en adelante</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>proj_condominio-parque-del-sur-torre-a</t>
+          <t>proj_condominio-francisco-zelada-torre-b</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Condominio Parque del Sur torre A</t>
+          <t>Edificio Francisco Zelada Torre B</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>La Cisterna</t>
+          <t>Estación Central</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Futura</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Aprobación</t>
+          <t>10% o lo que no financie el Banco</t>
         </is>
       </c>
       <c r="AG46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Pre Aprobación</t>
         </is>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>28/02/2026</t>
+          <t>47 (11+36)</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>1. Estacionamiento desde 2D/2B
- 2. Bodega desde 2D/1B
- 3. Deptos 202, 203, 207, 208 y 209 va con anexo 60 días
- 4. Solo disponibles linea 1, 3 y 6</t>
+          <t>En 47 cuotas (5% en 11 + 5% en 36):
+11 cuotas + 1 cuoton final con getnet hasta en 36 cuotas</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>31/03/2027</t>
+        </is>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Arriendo Asegurado 24m, Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI46" t="inlineStr">
+        <is>
+          <t>Estacionamiento y bodega solo para 2D/1B en adelante</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>proj_edificio-castillo-urizar</t>
+          <t>proj_edificio-guillermo-mann</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Edificio Castillo Urizar</t>
+          <t>Edificio Guillermo Mann</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -3022,302 +2950,435 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AG47" t="inlineStr">
+      <c r="AH47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF47" t="inlineStr">
-        <is>
-          <t>1. Estacionamiento y bodega obligatoria 
- 2. Depto 1110 no va con subsidio a la tasa
- 3. Todas las unidades llevan anexo 60 días</t>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>6 Dividendos Gratis, Arriendo Asegurado 24m, Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI47" t="inlineStr">
+        <is>
+          <t>1. Bodega y Estacionamiento obligatorio para departamentos 302-511-811
+2. Depto 302 va amoblado y 311 sala de ventas.
+3. Anexo de 60 días en todas las unidades</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>proj_edificio-guillermo-mann</t>
+          <t>proj_edificio-lia-aguirre</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Edificio Guillermo Mann</t>
+          <t>Edificio Lia Aguirre</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Ñuñoa</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AG48" t="inlineStr">
+      <c r="AH48" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF48" t="inlineStr">
-        <is>
-          <t>1. Bodega obligatoria
- 2. Estacionamiento tándem obligatorio desde 2D/1B en adelante
- 3. Todas las unidades llevan anexo 60 días
- 4. Deptos 302 se vende amoblado
- 5. Depto. 311 es sala de ventas</t>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>6 Dividendos Gratis, Arriendo Asegurado 24m, Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI48" t="inlineStr">
+        <is>
+          <t>1. Estacionamiento y bodega obligatoria
+2. Depto 209,210, 211,305 van con Anexo 60 Dias.
+3. Deptos 209,210,211 van con decoración.
+4. Deptos 903,1303,1305,1505 van con anexo de 90 días.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>proj_condominio-francisco-zelada-torre-b</t>
+          <t>proj_edificio-pedro-de-la-barra</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Condominio Francisco Zelada Torre B</t>
+          <t>Edificio Pedro de la Barra</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>Estacion central</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>FUTURA</t>
+          <t>Futura</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
           <t>Pre Aprobación</t>
         </is>
       </c>
-      <c r="AG49" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>54 (18+36)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>31-08-0202</t>
+          <t>38 (2+36)</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF49" t="inlineStr">
-        <is>
-          <t>1. Estacionamiento y bodega solo para 2D/1B en adelante</t>
+          <t>En 38 cuotas (3% en 2 + 7% en 36):
+2 cuota + 1 cuoton final con getnet hasta en 36 cuotas</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>6 Dividendos Gratis, Arriendo Asegurado 24m, Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI49" t="inlineStr">
+        <is>
+          <t>Estacionamiento y Bodega solo para  2D/ 2B 
+Deptos (306, 308, 309, 311) van con Anexo 60 Dias</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>proj_edificio-lia-aguirre</t>
+          <t>proj_edificio-trinidad-ramirez</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Edificio Lia Aguirre</t>
+          <t>Edificio Trinidad Ramirez</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>INMEDIATA</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
         <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AG50" t="inlineStr">
+      <c r="AH50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF50" t="inlineStr">
-        <is>
-          <t>1. Estacionamiento y bodega obligatoria
- 2. Depto 209,210, 211,305 va con Anexo 60 Dias</t>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI50" t="inlineStr">
+        <is>
+          <t>Estacionamiento debe ser vendido junto con la ultima unidad disponible
+2. Bodega obligatoria.
+3. Anexo de 60 días para todas las unidades</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>proj_edificio-pedro-de-la-barra</t>
+          <t>proj_alto-maranon-3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Edificio Pedro de la Barra</t>
+          <t>Alto Marañon 3</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Viña del Mar</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>FUTURA</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Pre Aprobación</t>
+          <t>10% o lo que no financie el Banco</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Aprobación</t>
         </is>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>43 (7+36)</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF51" t="inlineStr">
-        <is>
-          <t>1. Estacionamiento y bodega solo para 2D/2B
- 2. Deptos 306, 308, 309 y 311 van con anexo 60 días
- 3. Todas las lineas disponibles menos la 16</t>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI51" t="inlineStr">
+        <is>
+          <t>No se puede vender Estacionamiento ni bodegas por separado // Estacionamientos solo para 3D2B // Depto. 204 con anexo 60 dias</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>proj_parque-maranon-torre-a</t>
+          <t>proj_blanca-estela-i-torre-a</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PARQUE MARAÑON TORRE A</t>
+          <t>Edificio Blanca Estela Torre A</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Concon</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>ITAU</t>
-        </is>
-      </c>
-      <c r="BF52" t="inlineStr"/>
+          <t>Inmediata</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>Aprobación</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI52" t="inlineStr">
+        <is>
+          <t>No se puede vender mas de un estacionamiento por departamento</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>proj_blanca-estela-i-torre-a</t>
+          <t>proj_blanca-estela-i-torre-b</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BLANCA ESTELA I TORRE A Y B</t>
+          <t>Edificio Blanca Estela Torre B</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Concon</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>Banco de Chile</t>
-        </is>
-      </c>
-      <c r="BF53" t="inlineStr"/>
+          <t>Inmediata</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>Aprobación</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>GOP Gratis, Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI53" t="inlineStr">
+        <is>
+          <t>No se puede vender mas de un estacionamiento por departamento</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3327,7 +3388,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EDIFICIO PARQUE URBANO</t>
+          <t>Edificio Parque Urbano oficinas</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
@@ -3337,470 +3398,535 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
-        </is>
-      </c>
-      <c r="BF54" t="inlineStr"/>
+          <t>Inmediata</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>Aprobación</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>Pago con TC en 36 cuotas precio contado con getnet</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>GOP Gratis, 6 Dividendos Gratis, 24 Dividendos, Crédito Directo</t>
+        </is>
+      </c>
+      <c r="BI54" t="inlineStr">
+        <is>
+          <t>Estacionamiento y Bodega Obligatoria</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>proj_play</t>
+          <t>proj_parque-maranon-torre-a</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Parque Marañon Torre A</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Viña del Mar</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Futura</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>10% o lo que no financie el Banco</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>Aprobación</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>39 (3+36)</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>En 39 cuotas (5% en 3 + 5% en 36):
+3 cuotas + 1 cuoton final con getnet hasta en 36 cuotas</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>Entrega Inmediata</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Aprobación</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>UF 10</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>UF 50</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>* Toku *Getnet (hasta 24 cuotas sin intereses)</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr">
-        <is>
-          <t>Obligatorio (Excepción para estudio y 1D+1B)</t>
-        </is>
-      </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No obligatorio</t>
-        </is>
-      </c>
-      <c r="AV55" t="inlineStr">
-        <is>
-          <t>25% 1D+1D/Estudio 20% en el resto</t>
-        </is>
-      </c>
-      <c r="BF55" t="inlineStr"/>
+          <t>Crédito Directo, Knockit</t>
+        </is>
+      </c>
+      <c r="BI55" t="inlineStr">
+        <is>
+          <t>Estacionamiento y Bodega Obligatoria // Segunda Bodega 50 % de descuento</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>proj_fam</t>
+          <t>proj_play</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fam</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
+          <t>Play</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Entrega Inmediata</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AP56" t="inlineStr">
         <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>UF 10</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr">
+      <c r="AQ56" t="inlineStr">
+        <is>
+          <t>10 UF</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ56" t="inlineStr">
+      <c r="AT56" t="inlineStr">
         <is>
           <t>UF 50</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>* Toku *Getnet (hasta 36 cuotas sin intereses)</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>* Toku                                                                                                                                                                               *Getnet (hasta 24 cuotas sin intereses)</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>20% deptos y est.</t>
-        </is>
-      </c>
-      <c r="BF56" t="inlineStr"/>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Obligatorio (Excepción para estudio y 1D+1B)</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>No obligatorio</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>25% 1D+1D/Estudio                                                20% en el resto</t>
+        </is>
+      </c>
+      <c r="BI56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>proj_line</t>
+          <t>proj_fam</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
+          <t>Fam</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Entrega Inmediata</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
         <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>UF 10</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>10 UF</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="AP57" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ57" t="inlineStr">
+      <c r="AT57" t="inlineStr">
         <is>
           <t>UF 50</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>* Toku *Getnet (hasta 36 cuotas sin intereses)</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="AT57" t="inlineStr">
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>* Toku                                                                                                                                                                               *Getnet (hasta 36 cuotas sin intereses)</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
         <is>
           <t>Obligatorio</t>
         </is>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>Modelo C Obligatorio</t>
-        </is>
-      </c>
-      <c r="AV57" t="inlineStr">
-        <is>
-          <t>15% deptos</t>
-        </is>
-      </c>
-      <c r="BF57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>20% deptos y est.</t>
+        </is>
+      </c>
+      <c r="BI57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>proj_mind</t>
+          <t>proj_line</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mind</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Entrega Inmediata</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AP58" t="inlineStr">
         <is>
           <t>Aprobación</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>UF 10</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AQ58" t="inlineStr">
+        <is>
+          <t>10 UF</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="AP58" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ58" t="inlineStr">
+      <c r="AT58" t="inlineStr">
         <is>
           <t>UF 50</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>* Toku *Getnet (hasta 36 cuotas sin intereses)</t>
-        </is>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>28/02/2026</t>
-        </is>
-      </c>
-      <c r="AT58" t="inlineStr">
-        <is>
-          <t>Solo estos deptos 403/714/1701/1801 tienen derecho a estacionamiento</t>
-        </is>
-      </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2D+2B Opcional / 1D+1B No tiene derecho</t>
+          <t>* Toku                                                                                                                                                                               *Getnet (hasta 36 cuotas sin intereses)</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="BF58" t="inlineStr"/>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Obligatorio</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Modelo C Obligatorio</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>15% deptos</t>
+        </is>
+      </c>
+      <c r="BI58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>proj_parque-de-araya-torre-poniente</t>
+          <t>proj_mind</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PDA Torre Poniente</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>Venta en Verde</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Preaprobación</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>UF 10</t>
+          <t>Mind</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>Entrega Inmediata</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Aprobación</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>Pago de la primera cuota</t>
+          <t>10 UF</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>Toku</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>Estudio No tiene derecho</t>
+          <t>UF 50</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>* Toku                                                                                                                                                                               *Getnet (hasta 36 cuotas sin intereses)</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Solo estos deptos 714/1701/1801 tienen derecho a estacionamiento</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>2D+2B Opcional /                  1D+1B No tiene derecho</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="BF59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>proj_parque-de-araya-torre-oriente</t>
+          <t>proj_parque-de-araya-torre-poniente</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PDA Torre Oriente</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Venta en Verde</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Preaprobación</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>UF 10</t>
+          <t>PDA Torre Poniente</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
+          <t>Entrega Inmediata</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>Aprobación</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>10 UF</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>Pago de la primera cuota</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
+        <is>
+          <t>UF 50</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>Toku</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>28/01/2027</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr">
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Estudio No tiene derecho</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
         <is>
           <t>Obligatorio</t>
         </is>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>Obligatorio</t>
-        </is>
-      </c>
-      <c r="AV60" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="BF60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="BI60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>proj_status</t>
+          <t>proj_parque-de-araya-torre-oriente</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>STATUS, Stgo. Centro (SANTOLAYA)</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>Inmediata</t>
+          <t>PDA Torre Oriente</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Venta en Verde</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>Preaprobación</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr">
+        <is>
+          <t>10 UF</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="AS61" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr">
+        <is>
+          <t>Pago de la primera cuota</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>Toku</t>
+        </is>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>31/12/2026</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>249.000</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Inmediata</t>
+          <t>Obligatorio</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>1 a 3 cuotas TOKU / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="BF61" t="inlineStr">
-        <is>
-          <t>PROMOCION 24D (Bono pie 10%) Y 36D ( Bono pie 15%)(sujeto a valor tasación bco) (24D CUESTA 10% DESCTO, 36D CUESTA 15%) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · ULTIMOS 2 DEPTO DISP: 119 - 129 · VENTA OBLIGADA ESTAC Y BOD · ESTACIONAMIENTOS: 10% DESCTO · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto</t>
-        </is>
-      </c>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="BI61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>proj_suena-marin</t>
+          <t>proj_status</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SUEÑA MARIN, Stgo. Centro (SANTOLAYA)</t>
+          <t>STATUS, Stgo. Centro (SANTOLAYA)</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
@@ -3808,135 +3934,140 @@
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>218.000</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>249.000</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
         <is>
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
+      <c r="BB62" t="inlineStr">
         <is>
           <t>1 a 3 cuotas TOKU / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>17.4% / 20%</t>
-        </is>
-      </c>
-      <c r="BF62" t="inlineStr">
-        <is>
-          <t>PROMOCION 24D  (Bono Pie 10%) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · ULTIMOS 2 DEPTOS DISPONIBLES: 320 - 820 · VTA OBLIGADA BODEGA · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto · PROMOCION 24D</t>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="BI62" t="inlineStr">
+        <is>
+          <t>PROMOCION 24D (10% BONO PIE Y 36D (15% DE BONO PIE) (sujeto a valor tasación bco) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · ULTIMOS DEPTOS DISP: 129 · VENTA OBLIGADA ESTAC Y BOD · ESTACIONAMIENTOS: 10% DESCTO · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>proj_nodo-la-cisterna</t>
+          <t>proj_suena-marin</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NODO LA CISTERNA,  La Cisterna (DEISA)</t>
+          <t>SUEÑA MARIN, Stgo. Centro (SANTOLAYA)</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Futura</t>
-        </is>
-      </c>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>204.000</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>4to Trimestre 2027</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>22 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>218.000</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>Desde 7%</t>
+          <t>1 a 3 cuotas TOKU / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>1era cuota</t>
-        </is>
-      </c>
-      <c r="BD63" t="inlineStr">
-        <is>
-          <t>01/12/2027</t>
-        </is>
-      </c>
-      <c r="BF63" t="inlineStr">
-        <is>
-          <t>PROMOCION 24 DIVIDENDOS (10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 40 CUOTAS: LAS PRIMERAS 22 CUOTAS 7% CON TOKU + 18 C/TC  3% A LA ESCRITURA  + 10% 24D + 80% CH · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN</t>
+          <t>17.4% / 20%</t>
+        </is>
+      </c>
+      <c r="BI63" t="inlineStr">
+        <is>
+          <t>PROMOCION 24D  (10% BONO PIE) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · ULTIMOS 2 DEPTOS DISPONIBLES: 111 - 820 · VTA OBLIGADA BODEGA · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto · PROMOCION 24D (10% BONO PIE)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>proj_garden-macul</t>
+          <t>proj_nodo-la-cisterna</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GARDEN MACUL, Macul (SANTOLAYA)</t>
+          <t>NODO LA CISTERNA,  La Cisterna (DEISA)</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Inmediata</t>
-        </is>
-      </c>
-      <c r="AW64" t="inlineStr">
-        <is>
-          <t>227.000</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>Inmediata</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t>1 a 3 cuotas doc / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
+          <t>Futura</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>204.000</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>4to Trimestre 2027</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>20 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="BE64" t="inlineStr">
+        <is>
+          <t>Desde 7%</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>DEPTOS AGOTADOS, 4 ESTAC DISPONIBLES · OFERTA ESTAC TANDEM, ULTIMO : N°63-64  UF400 (75% DESCTO 2DA UNIDAD!!)</t>
+          <t>1era cuota</t>
+        </is>
+      </c>
+      <c r="BG64" t="inlineStr">
+        <is>
+          <t>01/12/2027</t>
+        </is>
+      </c>
+      <c r="BI64" t="inlineStr">
+        <is>
+          <t>PROMOCION 24 DIVIDENDOS  (10% BONO PIE) · PLAN ESPECIAL PIE EN HASTA 38 CUOTAS: 7% LAS PRIMERAS 20 CUOTAS CON TOKU + 3% EN 18 CUOTAS C/TC  A LA ESCRITURA  + 10% 24D + 80% CH · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>proj_ciudad-cerrillos</t>
+          <t>proj_suena-lincoyan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CIUDAD CERRILLOS, Cerrillos  (DEISA)</t>
+          <t>SUEÑA LINCOYAN, Ñuñoa (SANTOLAYA)</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
@@ -3944,46 +4075,41 @@
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AW65" t="inlineStr">
-        <is>
-          <t>209.000</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr">
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>219.000</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
         <is>
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>1 a 3 cuotas TOKU / ó 24 cuotas sin interés tarejta crédito (max 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>15%</t>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>1 a 3 cuotas / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="BF65" t="inlineStr">
-        <is>
-          <t>PROMOCION 24D (10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 27 CUOTAS: 2% CP + 1,5% EN HASTA 3 CUOTAS TOKU  + CUOTON 6,5% EN 24 C/TC · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · SIN ARRIENDO GARANTIZADO 2% DESCTO ADIC · ARRIENDO GARANTIZADO 2 AÑOS SOBRE MERCADO (REVISAR VALORES QUE APLICAN)</t>
+          <t>15% / 18%</t>
+        </is>
+      </c>
+      <c r="BI65" t="inlineStr">
+        <is>
+          <t>PROMOCION 24D · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · ULTIMO DEPTO DISPONIBLE: 110 · 2 AÑOS ARRIENDO GARANTIZADO -resta 2,5% descto · OPORTUNIDAD LOCALES DISPONIBLES (CORRESP A SV)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>proj_suena-lincoyan</t>
+          <t>proj_suena-toesca</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SUEÑA LINCOYAN, Ñuñoa (SANTOLAYA)</t>
+          <t>SUEÑA TOESCA, Stgo (SANTOLAYA)</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
@@ -3991,41 +4117,41 @@
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>219.000</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>226.000</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
         <is>
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t>1 a 3 cuotas / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="BF66" t="inlineStr">
-        <is>
-          <t>PROMOCION 24D  (10% de bono pie) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · 2 AÑOS ARRIENDO GARANTIZADO -resta 2,5% descto</t>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>1 a 3 cuotas  / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>15% / 20% / 24%</t>
+        </is>
+      </c>
+      <c r="BI66" t="inlineStr">
+        <is>
+          <t>PROMOCION 24D (10% BONO PIE) hasta 48D (20% BONO PIE) (APLICA PARA UNID SEGÚN TASACION) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · VTA OBLIGADA BODEGA · PLAN MAS CUOTAS: HASTA 5% EN 12 DOCUMENTADAS CON PAGARÉ POST ESCRITURA · 2 AÑOS ARRIENDO GARANTIZADO -resta 2,5% descto</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>proj_suena-toesca</t>
+          <t>proj_neoflorida-3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SUEÑA TOESCA, Stgo (SANTOLAYA)</t>
+          <t>NEO FLORIDA III. La florida (SANTOLAYA)</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
@@ -4033,41 +4159,41 @@
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>226.000</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>233.000</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
         <is>
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>1 a 3 cuotas  / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>15% / 20%</t>
-        </is>
-      </c>
-      <c r="BF67" t="inlineStr">
-        <is>
-          <t>PROMOCION 24D ( 10% de bono pie ) hasta 48D ( 20% de bono pie) (APLICA PARA UNID SEGÚN TASACION)  (24D CUESTA 10% DESCTO - 48D CUESTA 20% DESCTO) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · VTA OBLIGADA BODEGA · PLAN MAS CUOTAS: HASTA 5% EN 12 DOCUMENTADAS CON PAGARÉ POST ESCRITURA · 2 AÑOS ARRIENDO GARANTIZADO -resta 2,5% descto</t>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>1 a 3 cuotas / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>18% / 23%</t>
+        </is>
+      </c>
+      <c r="BI67" t="inlineStr">
+        <is>
+          <t>PROMOCION 24D(10 % BONO PIE  Y 36D 15% BONO PIE) (sujeto a valor tasación bco) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · VTA OBLIGADA BODEGA y ESTAC · 2 AÑOS ARRIENDO GARANTIZADO -resta 2,5% descto</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>proj_neoflorida-3</t>
+          <t>proj_ciudad-lyon</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NEO FLORIDA III. La florida (SANTOLAYA)</t>
+          <t>CIUDAD LYON, Providencia (DEISA)</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
@@ -4075,41 +4201,46 @@
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>233.000</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>229.000</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
         <is>
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AY68" t="inlineStr">
-        <is>
-          <t>1 a 3 cuotas / ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>18% / 23%</t>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>1 cuotas /ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>15%</t>
         </is>
       </c>
       <c r="BF68" t="inlineStr">
         <is>
-          <t>PROMOCION 24D( 10% de bono pie) Y 36D (15% de bono pie) (sujeto a valor tasación bco) · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · VTA OBLIGADA BODEGA</t>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="BI68" t="inlineStr">
+        <is>
+          <t>PROMOCION 12D · PLAN ESPECIAL PIE 7,5% CONTRA PROMESA - 7,5 CONTRA ESCRITURA 18 C/TC + 5% 12D + 80% CH · OPORTUNIDAD BX TANDEM UF550</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>proj_ciudad-lyon</t>
+          <t>proj_ciudad-cerrillos</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CIUDAD LYON, Providencia (DEISA)</t>
+          <t>CIUDAD CERRILLOS, Cerrillos  (DEISA)</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
@@ -4117,34 +4248,34 @@
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>229.000</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>209.000</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
         <is>
           <t>Inmediata</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t>1 cuotas /ó 18 cuotas sin interés tarjeta crédito (máx 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>15%</t>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>1 a 3 cuotas TOKU / ó 24 cuotas sin interés tarejta crédito (max 20% del precio)</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="BF69" t="inlineStr">
         <is>
-          <t>PROMOCION 12D (5% de bono pie) · PLAN ESPECIAL PIE 7,5% CONTRA PROMESA - 7,5 CONTRA ESCRITURA 18 C/TC + 5% 12D + 80% CH · OPORTUNIDAD: ULTIMA AZOTEA UF990</t>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="BI69" t="inlineStr">
+        <is>
+          <t>PROMOCION 24D (5% BONO PIE Y 10% BONO PIE SUJETO A TASACIÓN) · PLAN ESPECIAL PIE EN HASTA 27 CUOTAS: 2% CP + 1,5% EN HASTA 3 CUOTAS TOKU  + CUOTON 6,5% EN 24 C/TC + 24D + 80% CHIP · CREDITU: 5% RESTA 2% DESCTO  // 10% RESTA 4% DESCTO · SIN ARRIENDO GARANTIZADO 1,8% DESCTO ADIC · ARRIENDO GARANTIZADO 2 AÑOS SOBRE MERCADO (REVISAR VALORES QUE APLICAN)</t>
         </is>
       </c>
     </row>
@@ -4164,29 +4295,29 @@
           <t>PROXIMA ENTREGA</t>
         </is>
       </c>
-      <c r="AW70" t="inlineStr">
+      <c r="AZ70" t="inlineStr">
         <is>
           <t>220.000</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>21% / 24%</t>
-        </is>
-      </c>
-      <c r="BB70" t="inlineStr">
-        <is>
-          <t>Desde 2%</t>
-        </is>
-      </c>
       <c r="BC70" t="inlineStr">
         <is>
+          <t>23% / 27%</t>
+        </is>
+      </c>
+      <c r="BE70" t="inlineStr">
+        <is>
+          <t>Desde 1%</t>
+        </is>
+      </c>
+      <c r="BF70" t="inlineStr">
+        <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BF70" t="inlineStr">
-        <is>
-          <t>BONO PIE 10% - ASOCIADO A FIRMA PAGARÉ · PLAN ESPECIAL PIE EN 39 CUOTAS: 2% en 3 CUOTAS TOKU + 8% en 36 CUOTAS C/TC A LA ESCRITURA  + 10% 24D + 80% CREDITO · 2 CUPOS ESTAC PARA DPTO. 1,5D1B · 2 AÑOS ARRIENDO GARANTIZADO 1D Y 2D SOBRE MERCADO INCUIDO EN EL PRECIO · SI NO HAY ARRIENDO GARANTIZADO SE PUEDE DAR 4% DESC ADIC</t>
+      <c r="BI70" t="inlineStr">
+        <is>
+          <t>BONO PIE 10% - ASOCIADO A FIRMA PAGARÉ - 23% Y 24% MAXIMO CON AG · PROMOCION "DESDE PIE 0": 10% BONO PIE - 90% CHIP  (VTAS SIN $ CP, PAGO COMISION CONTRA ESCRITURA) · VENTA CON 90% CHIP Y FINANCIAMIENTO 5% CREDITU ESTA SUJETA A PRE-APROBACIÓN BCO Y CREDITU · ELIGE PROMOCION ADICIONAL: BONO DESCTO 3%  ó 5% CREDITU 60 MESES S/COSTO ó ARRIENDO GARANTIZADO NORMAL  2 AÑOS. · DEPTOS 1D Y 2D UNID SELECCIONADAS PRECIO FINAL: UF2.190 (1D) y UF2.790 (2D) (VER DETALLE DEPTOS HOJA ANEXA) (NO ACUMULA CON OTRAS PROMOC)</t>
         </is>
       </c>
     </row>
@@ -4206,44 +4337,44 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW71" t="inlineStr">
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>222.000</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
+      <c r="BA71" t="inlineStr">
         <is>
           <t>1er Trimestre 2028</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>25 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ71" t="inlineStr">
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>23 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="BB71" t="inlineStr">
+      <c r="BE71" t="inlineStr">
         <is>
           <t>Desde 7%</t>
         </is>
       </c>
-      <c r="BC71" t="inlineStr">
+      <c r="BF71" t="inlineStr">
         <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BD71" t="inlineStr">
+      <c r="BG71" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="BF71" t="inlineStr">
-        <is>
-          <t>PROMOCION 24 DIVIDENDOS(10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 43 CUOTAS: 7% LAS PRIMERAS 25 CUOTAS CON TOKU + 3% CUOTON CON 18 C/TC A LA ESCRITURA + 10% 24D + 80% CREDITO · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN</t>
+      <c r="BI71" t="inlineStr">
+        <is>
+          <t>PROMOCION 24 DIVIDENDOS · PLAN ESPECIAL PIE EN HASTA 41 CUOTAS: 7% LAS PRIMERAS 23 CUOTAS CON TOKU + 3% CON 18 CUOTAS C/TC A LA ESCRITURA + 10% 24D + 80% CREDITO · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN</t>
         </is>
       </c>
     </row>
@@ -4263,44 +4394,44 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW72" t="inlineStr">
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>228.000</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="BA72" t="inlineStr">
         <is>
           <t>1er Trimestre 2028</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr">
-        <is>
-          <t>25 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ72" t="inlineStr">
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>23 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="BB72" t="inlineStr">
+      <c r="BE72" t="inlineStr">
         <is>
           <t>Desde 7%</t>
         </is>
       </c>
-      <c r="BC72" t="inlineStr">
+      <c r="BF72" t="inlineStr">
         <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BD72" t="inlineStr">
+      <c r="BG72" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="BF72" t="inlineStr">
-        <is>
-          <t>PROMOCION 24 DIVIDENDOS (10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 43 CUOTAS: 7% LAS PRIMERAS 25 CUOTAS CON TOKU + 3% CUOTON CON 18 C/TC A LA ESCRITURA + 10% 24D + 80% CREDITO · SIN ARRIENDO GARANTIZADO 2% DESCTO ADICIONAL · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN · ARRIENDO GARANTIZADO SOBRE MERCADO 2 AÑOS INCLUIDO EN DESCTO MAX (REVISAR CONDICIONES Y VALORES QUE APLICAN)</t>
+      <c r="BI72" t="inlineStr">
+        <is>
+          <t>PROMOCION 24 DIVIDENDOS  (10% BONO PIE) · PLAN ESPECIAL PIE EN HASTA 41 CUOTAS: 7% LAS PRIMERAS 23 CUOTAS CON TOKU + 3% CON 18 CUOTAS C/TC A LA ESCRITURA + 10% 24D + 80% CREDITO · SIN ARRIENDO GARANTIZADO 2% DESCTO ADICIONAL · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN · ARRIENDO GARANTIZADO SOBRE MERCADO 2 AÑOS INCLUIDO EN DESCTO MAX (REVISAR CONDICIONES Y VALORES QUE APLICAN)</t>
         </is>
       </c>
     </row>
@@ -4320,44 +4451,44 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW73" t="inlineStr">
+      <c r="AZ73" t="inlineStr">
         <is>
           <t>230.000</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="BA73" t="inlineStr">
         <is>
           <t>1er Trimestre 2028</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>25 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>23 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="BB73" t="inlineStr">
+      <c r="BE73" t="inlineStr">
         <is>
           <t>Desde 7%</t>
         </is>
       </c>
-      <c r="BC73" t="inlineStr">
+      <c r="BF73" t="inlineStr">
         <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BD73" t="inlineStr">
+      <c r="BG73" t="inlineStr">
         <is>
           <t>01/03/2028</t>
         </is>
       </c>
-      <c r="BF73" t="inlineStr">
-        <is>
-          <t>PROMOCION 24 DIVIDENDOS (10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 43 CUOTAS - LAS PRIMERAS 25 CUOTAS 7% CON TOKU + 18 C/TC  3% A LA ESCRITURA  + 10% 24D + 80% CH · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN</t>
+      <c r="BI73" t="inlineStr">
+        <is>
+          <t>PROMOCION 24 DIVIDENDOS · PLAN ESPECIAL PIE EN HASTA 41 CUOTAS: 7% LAS PRIMERAS 23 CUOTAS CON TOKU + 3% CON 18 CUOTAS C/TC A LA ESCRITURA + 10% 24D + 80% CREDITO · PROMOCIÓN 1 AÑO DE GASTOS COMUNES GRATIS - NO RESTA DESCTO - REVISAR VALORES QUE APLICAN</t>
         </is>
       </c>
     </row>
@@ -4377,44 +4508,44 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW74" t="inlineStr">
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>203.000</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
+      <c r="BA74" t="inlineStr">
         <is>
           <t>01/06/2028</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>38 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 15% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ74" t="inlineStr">
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>36 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 15% del precio)</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
         <is>
           <t>15% / 20% / 5%</t>
         </is>
       </c>
-      <c r="BB74" t="inlineStr">
+      <c r="BE74" t="inlineStr">
         <is>
           <t>Desde 7%</t>
         </is>
       </c>
-      <c r="BC74" t="inlineStr">
+      <c r="BF74" t="inlineStr">
         <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BD74" t="inlineStr">
+      <c r="BG74" t="inlineStr">
         <is>
           <t>01/06/2028</t>
         </is>
       </c>
-      <c r="BF74" t="inlineStr">
-        <is>
-          <t>PROMOCION 24 DIVIDENDOS(10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 56 CUOTAS: LAS PRIMERAS 38 CUOTAS 7% CON TOKU + 18 C/TC 3% A LA ESCRITURA  + 10% 24D + 80% CH · 4 CUPOS ESTAC PARA DEPTOS 2D1B // 4 CUPOS BODEGA PARA DEPT 1D1B · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto · PLAN PAGO PIE LOCALES: 5% CP 15% EN CUOTAS - 5% C/E  - 75% CRED F Grales</t>
+      <c r="BI74" t="inlineStr">
+        <is>
+          <t>PROMOCION 24 DIVIDENDOS · PLAN ESPECIAL PIE EN HASTA 54 CUOTAS: 7% EN 36 CUOTAS CON TOKU + 3% EN 18 CUOTAS C/TC A LA ESCRITURA  + 10% 24D + 80% CH · 4 CUPOS ESTAC PARA DEPTOS 2D1B // 4 CUPOS BODEGA PARA DEPT 1D1B · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto · PLAN PAGO PIE LOCALES: 5% CP 15% EN CUOTAS - 5% C/E  - 75% CRED F Grales</t>
         </is>
       </c>
     </row>
@@ -4434,44 +4565,44 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW75" t="inlineStr">
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>208.000</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
+      <c r="BA75" t="inlineStr">
         <is>
           <t>1er Semestre 2027</t>
         </is>
       </c>
-      <c r="AY75" t="inlineStr">
-        <is>
-          <t>19 cuotas TOKU / ó 24 cuotas sin interés tarejta crédito (max 20% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ75" t="inlineStr">
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>21 cuotas TOKU / ó 24 cuotas sin interés tarejta crédito (max 20% del precio)</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="BB75" t="inlineStr">
-        <is>
-          <t>Desde 7%</t>
-        </is>
-      </c>
-      <c r="BC75" t="inlineStr">
+      <c r="BE75" t="inlineStr">
+        <is>
+          <t>Desde 5%</t>
+        </is>
+      </c>
+      <c r="BF75" t="inlineStr">
         <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BD75" t="inlineStr">
-        <is>
-          <t>01/08/2027</t>
-        </is>
-      </c>
-      <c r="BF75" t="inlineStr">
-        <is>
-          <t>BONO PIE 10%  - ASOCIADO A FIRMA PAGARÉ · PLAN ESPECIAL PIE EN HASTA 43 CUOTAS: LAS PRIMERAS 19 CUOTAS 7% CON TOKU + 24 C/TC  3% A LA ESCRITURA  + 10% 24D + 80% CH · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto</t>
+      <c r="BG75" t="inlineStr">
+        <is>
+          <t>01/12/2027</t>
+        </is>
+      </c>
+      <c r="BI75" t="inlineStr">
+        <is>
+          <t>BONO PIE 10% - ASOCIADO A FIRMA PAGARÉ · PLAN ESPECIAL PIE EN HASTA 45 CUOTAS: 5% EN 21 CUOTAS CON TOKU + 5% CON 24 CUOTAS C/TC  A LA ESCRITURA  + 10% 24D + 80% CH · 2 AÑOS ARRIENDO GARANTIZADO - resta 2,5% descto</t>
         </is>
       </c>
     </row>
@@ -4491,44 +4622,44 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW76" t="inlineStr">
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>211.000</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
+      <c r="BA76" t="inlineStr">
         <is>
           <t>2do semestre 2028</t>
         </is>
       </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>39 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 15% del precio)</t>
-        </is>
-      </c>
-      <c r="AZ76" t="inlineStr">
+      <c r="BB76" t="inlineStr">
+        <is>
+          <t>37 cuotas TOKU / ó 18 cuotas sin interés tarejta crédito (max 15% del precio)</t>
+        </is>
+      </c>
+      <c r="BC76" t="inlineStr">
         <is>
           <t>10% / 15%</t>
         </is>
       </c>
-      <c r="BB76" t="inlineStr">
+      <c r="BE76" t="inlineStr">
         <is>
           <t>Desde 7%</t>
         </is>
       </c>
-      <c r="BC76" t="inlineStr">
+      <c r="BF76" t="inlineStr">
         <is>
           <t>1era cuota</t>
         </is>
       </c>
-      <c r="BD76" t="inlineStr">
+      <c r="BG76" t="inlineStr">
         <is>
           <t>01/03/2029</t>
         </is>
       </c>
-      <c r="BF76" t="inlineStr">
-        <is>
-          <t>PROMOCION 24 DIVIDENDOS (10% de bono pie) · PLAN ESPECIAL PIE EN HASTA 57 CUOTAS:  LAS PRIMERAS 39 CUOTAS 7% CON TOKU + 18 C/TC 3% A LA ESCRITURA  + 10% 24D + 80% CH</t>
+      <c r="BI76" t="inlineStr">
+        <is>
+          <t>PROMOCION 24 DIVIDENDOS (10% BONO PIE) · PLAN ESPECIAL PIE EN HASTA 55 CUOTAS:  7% EN 37 CUOTAS CON TOKU + 3% CON 18 CUOTAS C/TC A LA ESCRITURA  + 10% 24D + 80% CH</t>
         </is>
       </c>
     </row>
@@ -4548,39 +4679,96 @@
           <t>Futura</t>
         </is>
       </c>
-      <c r="AW77" t="inlineStr">
+      <c r="AZ77" t="inlineStr">
         <is>
           <t>235.000</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1er Trimestre 2028</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t>22 cuotas TOKU / ó 36 cuotas sin interés tarjeta crédito (máx 20% del precio)(GETNET)</t>
-        </is>
-      </c>
-      <c r="AZ77" t="inlineStr">
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>1er Semestre 2028</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>20 cuotas TOKU / ó 36 cuotas sin interés tarjeta crédito (máx 20% del precio)(GETNET)</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="BB77" t="inlineStr">
+      <c r="BE77" t="inlineStr">
         <is>
           <t>13%</t>
         </is>
       </c>
-      <c r="BC77" t="inlineStr">
+      <c r="BF77" t="inlineStr">
         <is>
           <t>2%</t>
         </is>
       </c>
-      <c r="BF77" t="inlineStr">
-        <is>
-          <t>PAGO DEL PIE: 2% PROMESA + 13% EN 22 CUOTAS + 5% C/E ó 15% EN 22 CUOTAS + 5% C/E ó 10% EN 22 CUOTAS + 10% C/E + 80% CH</t>
+      <c r="BI77" t="inlineStr">
+        <is>
+          <t>PAGO DEL PIE: 2% PROMESA + 13% EN 20 CUOTAS + 5% C/E ó 15% EN 21 CUOTAS + 5% C/E ó 10% EN 21 CUOTAS + 10% C/E + 80% CH · (5% BONO PIE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>proj_porta-hurtado</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>PORTA HURTADO, Padre Hurtado  (70W)</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Pronta Entrega</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>202.000</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>1er Semestre 2026</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>2 cuotas TOKU / ó 36 cuotas sin interés tarjeta crédito (máx 20% del precio)(GETNET)</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="BE78" t="inlineStr">
+        <is>
+          <t>Desde 8%</t>
+        </is>
+      </c>
+      <c r="BF78" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="BG78" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="BI78" t="inlineStr">
+        <is>
+          <t>PLAN ESPECIAL PIE EN HASTA 38 CUOTAS: 2%CP + 8% EN 2 CUOTAS TOKU + 10% EN 36 C/TC CE + 80% CH</t>
         </is>
       </c>
     </row>

--- a/viveprop-platform/data/cc_data.xlsx
+++ b/viveprop-platform/data/cc_data.xlsx
@@ -1127,22 +1127,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alto Buzeta</t>
+          <t>Alto Buzeta (MT)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>09/02/2026</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>Cerrillos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.22%</t>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Creditú</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>3% 3D</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr"/>
@@ -1160,17 +1190,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>27/02/2024</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Max 10%</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr"/>
@@ -1183,22 +1238,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jardines de Alvarado</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>15/02/2023</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3.21</t>
+          <t>Jardines de Alvarado: solo tipología 3D1B (con descuento máximo de venta de 10%)</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr"/>
@@ -1211,17 +1251,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mirador Mapocho</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>08/05/2024</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Vivienda Social</t>
+          <t>Mirador Mapocho: solo tipología 1D1B (con descuento máximo de venta de 10%)</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr"/>
@@ -1239,17 +1269,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>06/07/2023</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>San Joaquín</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Max 10%</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr"/>
@@ -1267,17 +1322,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>03/04/2023</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Max 10%</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr"/>
@@ -1295,17 +1375,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03/04/2023</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Max 10%</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr"/>
@@ -1318,22 +1423,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Plaza Quilicura</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>24/02/2023</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>3.18</t>
+          <t>Plaza Quilicura: Se deben vender todos los departamentos con estacionamiento de manera obligatoria; Estacionamientos bajan a UF 250 (Precio anterior UF 290)</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr"/>
@@ -1351,17 +1441,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>31/12/2021</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>La Cisterna</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Max 10%</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr"/>
@@ -1374,22 +1489,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vista Costanera</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>14/09/2022</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>3.62</t>
+          <t>Vista Costanera: Bajan los estacionamientos a 2 x UF 500</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr"/>
@@ -1407,17 +1507,47 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>26/11/2024</t>
+          <t>Inmediata</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GOP</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Max 10%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2% 3D</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr"/>
